--- a/testData/authorTestTabTestData/authorTestCaseTab_testData.xlsx
+++ b/testData/authorTestTabTestData/authorTestCaseTab_testData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9216D26-3C69-4A37-A5B1-3340B4FFF198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B10A1E1-768D-4FB1-B39D-73B734A870EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6800" firstSheet="52" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6800" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddTest" sheetId="2" r:id="rId1"/>
